--- a/restored-src/UNAVAILABLE_FEATURES.xlsx
+++ b/restored-src/UNAVAILABLE_FEATURES.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17340"/>
+    <workbookView windowHeight="17340" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="工具类Stub" sheetId="1" r:id="rId1"/>
